--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -724,7 +736,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02324713824841671</v>
+        <v>0.02324713824841669</v>
       </c>
       <c r="J9" t="n">
         <v>523871</v>
@@ -761,7 +773,7 @@
         <v>86.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004299285744058736</v>
+        <v>0.004299285744058734</v>
       </c>
       <c r="J10" t="n">
         <v>657479</v>
@@ -773,81 +785,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="G11" t="n">
-        <v>3.33</v>
+        <v>1.53</v>
       </c>
       <c r="H11" t="n">
-        <v>88.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06371753035051776</v>
+        <v>0.9211493833547117</v>
       </c>
       <c r="J11" t="n">
-        <v>529715</v>
+        <v>42324</v>
       </c>
       <c r="K11" t="n">
-        <v>3624</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="F12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="G12" t="n">
-        <v>1.53</v>
+        <v>3.33</v>
       </c>
       <c r="H12" t="n">
-        <v>68.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9211493833547117</v>
+        <v>0.06371753035051776</v>
       </c>
       <c r="J12" t="n">
-        <v>42324</v>
+        <v>529715</v>
       </c>
       <c r="K12" t="n">
-        <v>4508</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -857,10 +869,10 @@
         <v>0.71</v>
       </c>
       <c r="D13" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -869,16 +881,16 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1000</v>
+        <v>3442</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -888,10 +900,10 @@
         <v>0.71</v>
       </c>
       <c r="D14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -900,10 +912,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>3442</v>
+        <v>1000</v>
       </c>
       <c r="K14" t="n">
-        <v>1031</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -934,7 +946,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4980193314692448</v>
+        <v>0.4980193314692444</v>
       </c>
       <c r="J15" t="n">
         <v>583089</v>
@@ -971,7 +983,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9601614254203767</v>
+        <v>0.9601614254203764</v>
       </c>
       <c r="J16" t="n">
         <v>307213</v>
@@ -983,69 +995,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="E17" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.09</v>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.001487604635598322</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>426489</v>
+        <v>456</v>
       </c>
       <c r="K17" t="n">
-        <v>19570</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.00148760463559832</v>
+      </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>426489</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="19">
@@ -1076,7 +1088,7 @@
         <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004106812827796202</v>
+        <v>0.004106812827796204</v>
       </c>
       <c r="J19" t="n">
         <v>678322</v>
@@ -1144,7 +1156,7 @@
         <v>77.7</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4473296420997004</v>
+        <v>0.4473296420997003</v>
       </c>
       <c r="J21" t="n">
         <v>739242</v>
@@ -1212,7 +1224,7 @@
         <v>57.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4784202102804351</v>
+        <v>0.4784202102804355</v>
       </c>
       <c r="J23" t="n">
         <v>1588466</v>
@@ -1348,7 +1360,7 @@
         <v>86.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5204776292170171</v>
+        <v>0.520477629217017</v>
       </c>
       <c r="J27" t="n">
         <v>737543</v>
@@ -1422,7 +1434,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B30" t="n">

--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,7 +822,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -832,10 +832,10 @@
         <v>0.71</v>
       </c>
       <c r="D12" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -844,16 +844,16 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>1000</v>
+        <v>3442</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -863,10 +863,10 @@
         <v>0.71</v>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -875,10 +875,10 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>3442</v>
+        <v>1000</v>
       </c>
       <c r="K13" t="n">
-        <v>1031</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
@@ -989,69 +989,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="E17" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.09</v>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.00148760463559832</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>426489</v>
+        <v>456</v>
       </c>
       <c r="K17" t="n">
-        <v>19570</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>70.59999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.00148760463559832</v>
+      </c>
       <c r="J18" t="n">
-        <v>456</v>
+        <v>426489</v>
       </c>
       <c r="K18" t="n">
-        <v>152</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="19">
@@ -1162,48 +1162,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="D22" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="E22" t="n">
         <v>1.09</v>
       </c>
       <c r="F22" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="G22" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="H22" t="n">
-        <v>57.3</v>
+        <v>79.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4784202102804355</v>
+        <v>0.3122522573644751</v>
       </c>
       <c r="J22" t="n">
-        <v>1588466</v>
+        <v>2268288</v>
       </c>
       <c r="K22" t="n">
-        <v>9351</v>
+        <v>41778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>0.97</v>
@@ -1215,72 +1215,78 @@
         <v>1.09</v>
       </c>
       <c r="F23" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="G23" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="H23" t="n">
-        <v>70.40000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8701326593934136</v>
+        <v>0.4784202102804355</v>
       </c>
       <c r="J23" t="n">
-        <v>380116</v>
+        <v>1588466</v>
       </c>
       <c r="K23" t="n">
-        <v>39052</v>
+        <v>9351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>choline</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="D24" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="E24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+        <v>1.09</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.37</v>
+      </c>
       <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8701326593934136</v>
+      </c>
       <c r="J24" t="n">
-        <v>159957</v>
+        <v>380116</v>
       </c>
       <c r="K24" t="n">
-        <v>526</v>
+        <v>39052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>choline</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="D25" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="E25" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1289,97 +1295,97 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>521911</v>
+        <v>159957</v>
       </c>
       <c r="K25" t="n">
-        <v>2012</v>
+        <v>526</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D26" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="E26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.4</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.520477629217017</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>737543</v>
+        <v>521911</v>
       </c>
       <c r="K26" t="n">
-        <v>6692</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="E27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+        <v>1.21</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.4</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>86.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.520477629217017</v>
+      </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>737543</v>
       </c>
       <c r="K27" t="n">
-        <v>1031</v>
+        <v>6692</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E28" t="n">
         <v>1.35</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.57</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1388,29 +1394,29 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>450</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="D29" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="E29" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1419,29 +1425,29 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>2108</v>
+        <v>1014</v>
       </c>
       <c r="K29" t="n">
-        <v>554</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E30" t="n">
         <v>1.92</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.47</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1450,29 +1456,29 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>7887</v>
+        <v>2108</v>
       </c>
       <c r="K30" t="n">
-        <v>103</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2.79</v>
+        <v>1.92</v>
       </c>
       <c r="D31" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="E31" t="n">
-        <v>4.88</v>
+        <v>2.47</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
@@ -1481,9 +1487,40 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
+        <v>7887</v>
+      </c>
+      <c r="K31" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dehydroepiandrosterone</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>200</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>100</v>
       </c>
     </row>

--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -541,12 +541,12 @@
       <c r="E2" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
       <c r="H2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="n"/>
       <c r="J2" s="8" t="n">
         <v>66450</v>
       </c>
@@ -582,7 +582,7 @@
         <v>92</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0.2282188608675651</v>
+        <v>0.2282188608675652</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>1947</v>
@@ -609,12 +609,12 @@
       <c r="E4" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n">
         <v>232908</v>
       </c>
@@ -640,12 +640,12 @@
       <c r="E5" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
         <v>360</v>
       </c>
@@ -671,12 +671,12 @@
       <c r="E6" s="5" t="n">
         <v>0.67</v>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="I6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n">
         <v>1906</v>
       </c>
@@ -702,12 +702,12 @@
       <c r="E7" s="5" t="n">
         <v>0.98</v>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n">
         <v>73909</v>
       </c>
@@ -733,12 +733,12 @@
       <c r="E8" s="5" t="n">
         <v>1.43</v>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="6" t="n">
         <v>86.7</v>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="n"/>
       <c r="J8" s="8" t="n">
         <v>63479</v>
       </c>
@@ -749,75 +749,75 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.73</v>
+        <v>4.94</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>86.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.004299285744058734</v>
+        <v>0.02324713824841671</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>657479</v>
+        <v>523871</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>30006</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>68.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.9211493833547111</v>
+        <v>0.004299285744058727</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>42324</v>
+        <v>657479</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>4508</v>
+        <v>30006</v>
       </c>
     </row>
     <row r="11">
@@ -848,7 +848,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.06371753035051778</v>
+        <v>0.06371753035051776</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>529715</v>
@@ -860,7 +860,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -870,28 +870,28 @@
         <v>0.71</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n">
-        <v>3442</v>
+        <v>1000</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1031</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -901,22 +901,22 @@
         <v>0.71</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="n"/>
       <c r="J13" s="8" t="n">
-        <v>1000</v>
+        <v>3442</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>500</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="14">
@@ -947,7 +947,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4980193314692444</v>
+        <v>0.4980193314692448</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>583089</v>
@@ -959,326 +959,320 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3.02</v>
+        <v>1.36</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.9259656898024045</v>
+        <v>0.00740548274572863</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>238872</v>
+        <v>611872</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>3158</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>omega-6_fatty_acids</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.09</v>
+      </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.8997360695254513</v>
+      </c>
       <c r="J16" s="8" t="n">
-        <v>6630</v>
+        <v>37261</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>3238</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
+        <v>1.03</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.85</v>
+      </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr"/>
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.1398697856494959</v>
+      </c>
       <c r="J17" s="8" t="n">
-        <v>456</v>
+        <v>723200</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>152</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.91</v>
+        <v>1.07</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.09</v>
+        <v>2.37</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>70.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.001487604635598321</v>
+        <v>0.9601614254203767</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>426489</v>
+        <v>307213</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>19570</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>omega-6_fatty_acids</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>1.17</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="6" t="n">
-        <v>76</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>0.004106812827796201</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n"/>
       <c r="J19" s="8" t="n">
-        <v>678322</v>
+        <v>6630</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>30201</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>1.8</v>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="6" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0.2934998479789542</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n"/>
       <c r="J20" s="8" t="n">
-        <v>712037</v>
+        <v>456</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>10452</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C21" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>0.92</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.06</v>
+      </c>
       <c r="H21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="7" t="inlineStr"/>
+        <v>69.2</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0008814538627601186</v>
+      </c>
       <c r="J21" s="8" t="n">
-        <v>82948</v>
+        <v>492939</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>696</v>
+        <v>20434</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1.56</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
       <c r="H22" s="6" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0.312252257364475</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n"/>
       <c r="J22" s="8" t="n">
-        <v>2268288</v>
+        <v>66450</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>41778</v>
+        <v>864</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1.31</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
       <c r="H23" s="6" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>0.4784202102804354</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="n"/>
       <c r="J23" s="8" t="n">
-        <v>1588466</v>
+        <v>82948</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>9351</v>
+        <v>696</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>0.97</v>
@@ -1290,280 +1284,354 @@
         <v>1.09</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>70.40000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.8701326593934136</v>
+        <v>0.4784202102804352</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>380116</v>
+        <v>1588466</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>39052</v>
+        <v>9351</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>choline</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>0.98</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.57</v>
+      </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="7" t="inlineStr"/>
+        <v>79.7</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.3880140653428208</v>
+      </c>
       <c r="J25" s="8" t="n">
-        <v>159957</v>
+        <v>2398895</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>526</v>
+        <v>44419</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>choline</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="n">
-        <v>521911</v>
+        <v>159957</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>2012</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>86.2</v>
+        <v>72.2</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.520477629217017</v>
+        <v>0.6526141509363801</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>737543</v>
+        <v>446566</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>6692</v>
+        <v>39916</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1.14</v>
+        <v>0.97</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
+        <v>1.05</v>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
-        <v>0</v>
+        <v>521911</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1031</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
+        <v>1.18</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.34</v>
+      </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="7" t="inlineStr"/>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.670221817796779</v>
+      </c>
       <c r="J29" s="8" t="n">
-        <v>1014</v>
+        <v>896626</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>450</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
+        <v>1.35</v>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
       <c r="H30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n">
-        <v>2108</v>
+        <v>0</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>554</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
+        <v>1.57</v>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
       <c r="H31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n">
-        <v>7887</v>
+        <v>1014</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>103</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="8" t="n">
+        <v>2108</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="8" t="n">
+        <v>7887</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>dehydroepiandrosterone</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5" t="n">
         <v>2.79</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D34" s="5" t="n">
         <v>1.22</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E34" s="5" t="n">
         <v>4.88</v>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="8" t="n">
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K32" s="8" t="n">
+      <c r="K34" s="8" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K32"/>
+  <autoFilter ref="A1:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -582,7 +582,7 @@
         <v>92</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0.2282188608675652</v>
+        <v>0.2282188608675651</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>1947</v>
@@ -774,7 +774,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.02324713824841671</v>
+        <v>0.0232471382484167</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>523871</v>
@@ -811,7 +811,7 @@
         <v>86.5</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.004299285744058727</v>
+        <v>0.004299285744058734</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>657479</v>
@@ -848,7 +848,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.06371753035051776</v>
+        <v>0.06371753035051778</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>529715</v>
@@ -947,7 +947,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4980193314692448</v>
+        <v>0.4980193314692444</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>583089</v>
@@ -984,7 +984,7 @@
         <v>69.3</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.00740548274572863</v>
+        <v>0.007405482745728637</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>611872</v>
@@ -1021,7 +1021,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.8997360695254513</v>
+        <v>0.899736069525451</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>37261</v>
@@ -1058,7 +1058,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.1398697856494959</v>
+        <v>0.1398697856494957</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>723200</v>
@@ -1095,7 +1095,7 @@
         <v>90.09999999999999</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.9601614254203767</v>
+        <v>0.9601614254203765</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>307213</v>
@@ -1194,7 +1194,7 @@
         <v>69.2</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0008814538627601186</v>
+        <v>0.0008814538627601165</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>492939</v>
@@ -1293,7 +1293,7 @@
         <v>57.3</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.4784202102804352</v>
+        <v>0.4784202102804354</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>1588466</v>
@@ -1330,7 +1330,7 @@
         <v>79.7</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.3880140653428208</v>
+        <v>0.3880140653428211</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>2398895</v>
@@ -1466,7 +1466,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.670221817796779</v>
+        <v>0.6702218177967789</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>896626</v>

--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -526,88 +526,88 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
+        <v>0.93</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>7452916.73</v>
+      </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7" t="n"/>
+        <v>92</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0.2282188608675651</v>
+      </c>
       <c r="J2" s="8" t="n">
-        <v>66450</v>
+        <v>1947</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>25509</v>
+        <v>768</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>7452916.73</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>0.2282188608675651</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="n"/>
       <c r="J3" s="8" t="n">
-        <v>1947</v>
+        <v>232908</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>768</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>lactobacillus</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -616,171 +616,177 @@
       </c>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="8" t="n">
-        <v>232908</v>
+        <v>360</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>1110</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>lactobacillus</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
-        <v>360</v>
+        <v>1906</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>176</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>vitamin_b6</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="8" t="n">
-        <v>1906</v>
+        <v>73909</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>754</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>vitamin_b6</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.98</v>
+        <v>1.43</v>
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n">
-        <v>73909</v>
+        <v>63479</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>104</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
+        <v>0.99</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.94</v>
+      </c>
       <c r="H8" s="6" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="I8" s="7" t="n"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0232471382484167</v>
+      </c>
       <c r="J8" s="8" t="n">
-        <v>63479</v>
+        <v>523871</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>506</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>4.94</v>
+        <v>3.33</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>85.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.0232471382484167</v>
+        <v>0.06371753035051778</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>523871</v>
+        <v>529715</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>2791</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="10">
@@ -790,77 +796,71 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>86.5</v>
+        <v>87.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.004299285744058734</v>
+        <v>0.01413592378341302</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>657479</v>
+        <v>591029</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>30006</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>mushrooms</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>3.33</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="6" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>0.06371753035051778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="n"/>
       <c r="J11" s="8" t="n">
-        <v>529715</v>
+        <v>1000</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>3624</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>mushrooms</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -870,10 +870,10 @@
         <v>0.71</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
@@ -882,115 +882,121 @@
       </c>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="8" t="n">
-        <v>1000</v>
+        <v>3442</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>500</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+        <v>1.29</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>945.6900000000001</v>
+      </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="7" t="n"/>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.4980193314692444</v>
+      </c>
       <c r="J13" s="8" t="n">
-        <v>3442</v>
+        <v>583089</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1031</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>0.41</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" s="5" t="n">
-        <v>945.6900000000001</v>
+        <v>1.36</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>91.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.4980193314692444</v>
+        <v>0.007405482745728637</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>583089</v>
+        <v>611872</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>2528</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0.74</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>69.3</v>
+        <v>63</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.007405482745728637</v>
+        <v>0.02356329011116449</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>611872</v>
+        <v>68361</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>4692</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="16">
@@ -1169,100 +1175,106 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1.06</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
       <c r="H21" s="6" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>0.0008814538627601165</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I21" s="7" t="n"/>
       <c r="J21" s="8" t="n">
-        <v>492939</v>
+        <v>82948</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>20434</v>
+        <v>696</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
+        <v>1.14</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.64</v>
+      </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n"/>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.854887127293174</v>
+      </c>
       <c r="J22" s="8" t="n">
-        <v>66450</v>
+        <v>336054</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>864</v>
+        <v>38479</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.7</v>
+      </c>
       <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7" t="n"/>
+        <v>79</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.4001749953490507</v>
+      </c>
       <c r="J23" s="8" t="n">
-        <v>82948</v>
+        <v>832445</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>696</v>
+        <v>18046</v>
       </c>
     </row>
     <row r="24">
@@ -1305,57 +1317,51 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>choline</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>0.98</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1.57</v>
-      </c>
+        <v>1.31</v>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
       <c r="H25" s="6" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>0.3880140653428211</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="n"/>
       <c r="J25" s="8" t="n">
-        <v>2398895</v>
+        <v>159957</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>44419</v>
+        <v>526</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>choline</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
@@ -1364,66 +1370,66 @@
       </c>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="8" t="n">
-        <v>159957</v>
+        <v>521911</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>526</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.7</v>
+        <v>0.87</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>72.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.6526141509363801</v>
+        <v>0.6702218177967789</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>446566</v>
+        <v>896626</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>39916</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1432,66 +1438,60 @@
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="8" t="n">
-        <v>521911</v>
+        <v>0</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>2012</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1.34</v>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
       <c r="H29" s="6" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>0.6702218177967789</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I29" s="7" t="n"/>
       <c r="J29" s="8" t="n">
-        <v>896626</v>
+        <v>1014</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>4800</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
@@ -1500,29 +1500,29 @@
       </c>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="8" t="n">
-        <v>0</v>
+        <v>2108</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1031</v>
+        <v>554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.35</v>
+        <v>2.79</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.57</v>
+        <v>4.88</v>
       </c>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
@@ -1531,107 +1531,14 @@
       </c>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="8" t="n">
-        <v>1014</v>
+        <v>200</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>fermented_foods</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="8" t="n">
-        <v>2108</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>iron</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="8" t="n">
-        <v>7887</v>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>dehydroepiandrosterone</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K34" s="8" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -533,25 +533,25 @@
         <v>3</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>7452916.73</v>
+        <v>21906296.98</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>0.2282188608675651</v>
+        <v>0.2322830305626233</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>1947</v>
@@ -570,10 +570,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0.98</v>
@@ -601,13 +601,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
@@ -632,18 +632,18 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="8" t="n">
@@ -663,10 +663,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0.98</v>
@@ -694,18 +694,18 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="6" t="n">
-        <v>86.7</v>
+        <v>88.2</v>
       </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="8" t="n">
@@ -725,25 +725,25 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.99</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>4.94</v>
+        <v>5.9</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>85.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0232471382484167</v>
+        <v>0.02483136601905617</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>523871</v>
@@ -762,25 +762,25 @@
         <v>4</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0.98</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>3.33</v>
+        <v>3.83</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>88.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.06371753035051778</v>
+        <v>0.06078493414255114</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>529715</v>
@@ -799,25 +799,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>87.2</v>
+        <v>87.8</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.01413592378341302</v>
+        <v>0.0130472561502979</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>591029</v>
@@ -836,13 +836,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
@@ -867,13 +867,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
@@ -898,10 +898,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>1.29</v>
@@ -910,13 +910,13 @@
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>945.6900000000001</v>
+        <v>1353.96</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>91.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.4980193314692444</v>
+        <v>0.4971204258671445</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>583089</v>
@@ -935,25 +935,25 @@
         <v>8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>69.3</v>
+        <v>71.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.007405482745728637</v>
+        <v>0.006737992167500233</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>611872</v>
@@ -965,75 +965,75 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.23</v>
+        <v>2.82</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>63</v>
+        <v>70.3</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.02356329011116449</v>
+        <v>0.7877261024144055</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>68361</v>
+        <v>37261</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>5262</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3.09</v>
+        <v>1.25</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>75.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.899736069525451</v>
+        <v>0.02305109437704161</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>37261</v>
+        <v>68361</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>2041</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="17">
@@ -1046,25 +1046,25 @@
         <v>8</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.1398697856494957</v>
+        <v>0.1368143494983235</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>723200</v>
@@ -1083,25 +1083,25 @@
         <v>8</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.9601614254203765</v>
+        <v>0.6980065255140948</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>307213</v>
@@ -1120,13 +1120,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
@@ -1151,13 +1151,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
@@ -1182,13 +1182,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
@@ -1213,25 +1213,25 @@
         <v>11</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>71.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.854887127293174</v>
+        <v>0.8424433015631739</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>336054</v>
@@ -1250,25 +1250,25 @@
         <v>20</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.4001749953490507</v>
+        <v>0.3505639908184721</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>832445</v>
@@ -1296,16 +1296,16 @@
         <v>1.09</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.4784202102804354</v>
+        <v>0.4623089467253695</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>1588466</v>
@@ -1389,22 +1389,22 @@
         <v>1.08</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.6702218177967789</v>
+        <v>0.7089254682310198</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>896626</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
@@ -1454,13 +1454,13 @@
         <v>1</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
@@ -1485,13 +1485,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
@@ -1516,13 +1516,13 @@
         <v>1</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2.79</v>
+        <v>3.67</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4.88</v>
+        <v>10.2</v>
       </c>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>

--- a/Plot/exposures_meta_analysis_ovarian_combined.xlsx
+++ b/Plot/exposures_meta_analysis_ovarian_combined.xlsx
@@ -545,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>21906296.98</v>
+        <v>21906296.97</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>92.2</v>
@@ -743,7 +743,7 @@
         <v>86.7</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.02483136601905617</v>
+        <v>0.02483136601905619</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>523871</v>
@@ -780,7 +780,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.06078493414255114</v>
+        <v>0.06078493414255117</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>529715</v>
@@ -817,7 +817,7 @@
         <v>87.8</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0130472561502979</v>
+        <v>0.01304725615029791</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>591029</v>
@@ -916,7 +916,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.4971204258671445</v>
+        <v>0.497120425867145</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>583089</v>
@@ -953,7 +953,7 @@
         <v>71.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.006737992167500233</v>
+        <v>0.006737992167500238</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>611872</v>
@@ -990,7 +990,7 @@
         <v>70.3</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.7877261024144055</v>
+        <v>0.787726102414406</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>37261</v>
@@ -1027,7 +1027,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.02305109437704161</v>
+        <v>0.02305109437704168</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>68361</v>
@@ -1064,7 +1064,7 @@
         <v>77.7</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.1368143494983235</v>
+        <v>0.1368143494983236</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>723200</v>
@@ -1101,7 +1101,7 @@
         <v>90</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.6980065255140948</v>
+        <v>0.6980065255140946</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>307213</v>
@@ -1231,7 +1231,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.8424433015631739</v>
+        <v>0.8424433015631738</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>336054</v>
@@ -1305,7 +1305,7 @@
         <v>57.6</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.4623089467253695</v>
+        <v>0.4623089467253692</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>1588466</v>
@@ -1404,7 +1404,7 @@
         <v>84.3</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.7089254682310198</v>
+        <v>0.70892546823102</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>896626</v>
